--- a/public/templates/AMC_컨센서스_양식.xlsx
+++ b/public/templates/AMC_컨센서스_양식.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,17 @@
       <sz val="15"/>
     </font>
     <font>
+      <color rgb="003A4452"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
       <color rgb="005A6678"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -44,7 +53,7 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="009AA3B2"/>
+      <color rgb="008A8A8A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -53,7 +62,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -67,7 +76,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBFBF5"/>
+        <fgColor rgb="0025406B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,25 +121,52 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -205,9 +251,14 @@
     <author>guide</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>강세 / 중립 / 약세 중 선택</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>예시 행입니다(참고용). 입력은 아래 칸에 하세요.</t>
       </text>
     </comment>
   </commentList>
@@ -220,9 +271,14 @@
     <author>guide</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>매수 / 중립 / 매도 중 선택</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>예시 행입니다(참고용). 입력은 아래 칸에 하세요.</t>
       </text>
     </comment>
   </commentList>
@@ -235,9 +291,14 @@
     <author>guide</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>강세 / 중립 / 약세 중 선택</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>예시 행입니다(참고용). 입력은 아래 칸에 하세요.</t>
       </text>
     </comment>
   </commentList>
@@ -533,10 +594,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="95" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,7 +613,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>■ 군인공제회 증권운용1팀 — 위탁운용사(AMC) 증시 컨센서스 제출 양식입니다.</t>
+          <t>군인공제회 증권운용1팀 — 위탁운용사(AMC) 증시 컨센서스 제출 양식입니다.</t>
         </is>
       </c>
     </row>
@@ -562,63 +623,63 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1) 아래 3개 시트를 작성해 주세요:  [국내시장]  [국내종목]  [해외]</t>
+          <t>작성 방법</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2) 색이 옅은 (예시) 행은 참고용입니다. 지우고 그 아래부터 작성하시거나, 덮어쓰셔도 됩니다.</t>
+          <t xml:space="preserve">  1. 아래 3개 시트를 채워 주세요:  [국내시장]  [국내종목]  [해외]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>3) 회색 음영 셀(방향성/의견)은 클릭하면 드롭다운으로 선택할 수 있습니다.</t>
+          <t xml:space="preserve">  2. 각 시트의 옅은 노란색 행은 "작성 예시"입니다(참고용, 수정 불필요).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 방향성 = 강세 / 중립 / 약세</t>
+          <t xml:space="preserve">     실제 입력은 그 아래 흰색 칸에 하시면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 의견   = 매수 / 중립 / 매도</t>
+          <t xml:space="preserve">  3. 방향성(강세/중립/약세), 의견(매수/중립/매도)은 칸을 클릭하면 나오는 드롭다운에서 선택합니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>4) 목표밴드는 지수의 예상 하단~상단을 숫자로 입력합니다. (예: KOSPI 2,700 ~ 3,000)</t>
+          <t xml:space="preserve">  4. 목표밴드는 지수의 예상 하단~상단을 숫자로 입력합니다(천단위 콤마 자동).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>5) Pro(긍정사유) / Con(부정사유)는 핵심만 간결히 적어 주세요.</t>
+          <t xml:space="preserve">  5. [국내종목]은 운용사가 자유 선정한 Top Pick을 적습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>6) [국내종목]은 운용사가 자유롭게 선정한 Top Pick 종목을 적습니다(행 수 제한 없음).</t>
+          <t xml:space="preserve">  6. [해외]는 미국/일본/베트남/인도/ACWI/선진국 6개 시장이 미리 채워져 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>7) [해외] 시장은 미국 / 일본 / 베트남 / 인도 / ACWI / 선진국 6개가 기본 제공됩니다.</t>
+          <t xml:space="preserve">     각 행에 운용사명·작성일·방향성·목표·Pro/Con만 채우시면 됩니다.</t>
         </is>
       </c>
     </row>
@@ -628,7 +689,45 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>※ 작성 후 파일을 그대로 담당자에게 회신하시면 됩니다. (파일명은 자유)</t>
+          <t>입력 보호</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 입력 칸 외에는 잠겨 있어 실수로 양식이 깨지지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 행을 추가하는 등 양식을 바꿔야 하면: 상단 [검토] 탭 → [시트 보호 해제](암호 없음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>제출</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 작성 후 파일을 그대로 담당자에게 회신하시면 됩니다(파일명 자유).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 운용사명은 각 시트의 모든 입력 행에 적어 주세요(여러 파일을 한 번에 취합합니다).</t>
         </is>
       </c>
     </row>
@@ -643,91 +742,164 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
+          <t>국내 증시 전망 (운용사당 1행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>방향성·의견은 드롭다운에서 선택하세요. 옅은 노란색 행은 작성 예시(참고용)이며 입력은 그 아래 칸에 하시면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>운용사명</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>작성일</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>방향성</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>KOSPI 목표 하단</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>KOSPI 목표 상단</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Pro (긍정사유)</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Con (부정사유)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>(예시) 미래에셋자산운용</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D4" s="7" t="n">
         <v>2750</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E4" s="7" t="n">
         <v>3050</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>반도체 업황 회복, 외국인 순매수 전환</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>미국 금리 인하 지연, 중국 둔화</t>
         </is>
       </c>
     </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n"/>
+    </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 값 확인" error="목록에서 선택하세요: 강세 / 중립 / 약세" promptTitle="선택" prompt="강세 / 중립 / 약세 중 선택" type="list">
+    <dataValidation sqref="C5:C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 값 확인" error="목록에서 선택: 강세 / 중립 / 약세" promptTitle="선택" prompt="강세 / 중립 / 약세 중 선택" type="list">
       <formula1>"강세,중립,약세"</formula1>
     </dataValidation>
   </dataValidations>
@@ -742,84 +914,261 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
+          <t>국내 종목 매수/매도 의견 (자유 선정 Top Pick)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>방향성·의견은 드롭다운에서 선택하세요. 옅은 노란색 행은 작성 예시(참고용)이며 입력은 그 아래 칸에 하시면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>운용사명</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>의견</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>사유</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>(예시) 미래에셋자산운용</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>매수</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>HBM 경쟁력 회복, 메모리 업황 반등</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>(예시) 미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>매수</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>AI 수요 수혜, HBM 시장 선두</t>
-        </is>
-      </c>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="8" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="8" t="n"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="8" t="n"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="8" t="n"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="8" t="n"/>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="11" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 값 확인" error="목록에서 선택하세요: 매수 / 중립 / 매도" promptTitle="선택" prompt="매수 / 중립 / 매도 중 선택" type="list">
+    <dataValidation sqref="C5:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 값 확인" error="목록에서 선택: 매수 / 중립 / 매도" promptTitle="선택" prompt="매수 / 중립 / 매도 중 선택" type="list">
       <formula1>"매수,중립,매도"</formula1>
     </dataValidation>
   </dataValidations>
@@ -834,227 +1183,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
+          <t>해외 증시 전망 (시장별)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>방향성·의견은 드롭다운에서 선택하세요. 옅은 노란색 행은 작성 예시(참고용)이며 입력은 그 아래 칸에 하시면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>운용사명</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>작성일</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>기준지수</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>방향성</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>목표 하단</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>목표 상단</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Pro (긍정사유)</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Con (부정사유)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>(예시) 미래에셋자산운용</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>미국</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>S&amp;P500</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F4" s="7" t="n">
         <v>5400</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G4" s="7" t="n">
         <v>6000</v>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>AI 투자 사이클 지속</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>밸류에이션 부담</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr"/>
-      <c r="B3" s="6" t="inlineStr"/>
-      <c r="C3" s="7" t="inlineStr">
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>미국</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>S&amp;P500</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="6" t="inlineStr"/>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr"/>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>일본</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Nikkei225</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>베트남</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>VN-Index</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>인도</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Nifty50</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>ACWI</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>MSCI ACWI</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr"/>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>선진국</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>MSCI World</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 값 확인" error="목록에서 선택하세요: 강세 / 중립 / 약세" promptTitle="선택" prompt="강세 / 중립 / 약세 중 선택" type="list">
+    <dataValidation sqref="E5:E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 값 확인" error="목록에서 선택: 강세 / 중립 / 약세" promptTitle="선택" prompt="강세 / 중립 / 약세 중 선택" type="list">
       <formula1>"강세,중립,약세"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/templates/AMC_컨센서스_양식.xlsx
+++ b/public/templates/AMC_컨센서스_양식.xlsx
@@ -173,6 +173,50 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00C0392B"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="005A6678"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00ECEEF1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="001F5FBF"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E4ECFB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFD4D4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -251,6 +295,16 @@
     <author>guide</author>
   </authors>
   <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>운용사명은 이 행(첫 입력칸)에만 적으면 됩니다. 한 운용사가 한 파일을 작성합니다.</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>날짜 형식 예: 2026-06-20</t>
+      </text>
+    </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>강세 / 중립 / 약세 중 선택</t>
@@ -271,6 +325,11 @@
     <author>guide</author>
   </authors>
   <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>운용사명은 첫 종목 행에만 적으면 됩니다. 아래 종목들은 자동으로 같은 운용사로 인식됩니다.</t>
+      </text>
+    </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>매수 / 중립 / 매도 중 선택</t>
@@ -291,6 +350,16 @@
     <author>guide</author>
   </authors>
   <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>운용사명은 첫 행에만 적으면 됩니다(아래 행 자동 인식).</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>날짜 형식 예: 2026-06-20</t>
+      </text>
+    </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>강세 / 중립 / 약세 중 선택</t>
@@ -299,6 +368,11 @@
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
         <t>예시 행입니다(참고용). 입력은 아래 칸에 하세요.</t>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0">
+      <text>
+        <t>기본 6개 시장 외에 추가할 시장이 있으면 이 아래 빈 칸에 직접 입력하세요.</t>
       </text>
     </comment>
   </commentList>
@@ -594,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -658,76 +732,104 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. 목표밴드는 지수의 예상 하단~상단을 숫자로 입력합니다(천단위 콤마 자동).</t>
+          <t xml:space="preserve">     선택하면 칸 색이 바뀝니다 — 강세·매수=빨강, 중립=회색, 약세·매도=파랑.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. [국내종목]은 운용사가 자유 선정한 Top Pick을 적습니다.</t>
+          <t xml:space="preserve">  4. 목표밴드는 지수의 예상 하단~상단을 숫자로 입력합니다(천단위 콤마 자동).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. [해외]는 미국/일본/베트남/인도/ACWI/선진국 6개 시장이 미리 채워져 있습니다.</t>
+          <t xml:space="preserve">     상단이 하단보다 작으면 두 칸이 빨갛게 표시되니 값을 확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">     각 행에 운용사명·작성일·방향성·목표·Pro/Con만 채우시면 됩니다.</t>
+          <t xml:space="preserve">  5. [국내종목]은 운용사가 자유 선정한 Top Pick을 적습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. [해외]는 미국/일본/베트남/인도/ACWI/선진국 6개 시장이 미리 채워져 있습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>입력 보호</t>
+          <t xml:space="preserve">     각 행에 운용사명·작성일·방향성·목표·Pro/Con만 채우시면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 입력 칸 외에는 잠겨 있어 실수로 양식이 깨지지 않습니다.</t>
+          <t xml:space="preserve">     6개 외 추가 시장은 그 아래 빈 칸에 직접 입력하면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · 행을 추가하는 등 양식을 바꿔야 하면: 상단 [검토] 탭 → [시트 보호 해제](암호 없음).</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>입력 보호</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>제출</t>
+          <t xml:space="preserve">  · 입력 칸 외에는 잠겨 있어 실수로 양식이 깨지지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  · 행을 추가하는 등 양식을 바꿔야 하면: 상단 [검토] 탭 → [시트 보호 해제](암호 없음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>제출</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  · 작성 후 파일을 그대로 담당자에게 회신하시면 됩니다(파일명 자유).</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · 운용사명은 각 시트의 모든 입력 행에 적어 주세요(여러 파일을 한 번에 취합합니다).</t>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 운용사명은 각 시트의 "첫 입력 행"에만 적으면 됩니다. 이어지는 행은 자동으로 같은</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    운용사로 인식됩니다. (한 파일은 한 운용사가 작성하는 것을 기준으로 합니다.)</t>
         </is>
       </c>
     </row>
@@ -898,6 +1000,22 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
+  <conditionalFormatting sqref="C5:C10">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"강세"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"중립"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"약세"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:E10">
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>AND($D5&lt;&gt;"",$E5&lt;&gt;"",$E5&lt;$D5)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="C5:C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 값 확인" error="목록에서 선택: 강세 / 중립 / 약세" promptTitle="선택" prompt="강세 / 중립 / 약세 중 선택" type="list">
       <formula1>"강세,중립,약세"</formula1>
@@ -1167,6 +1285,17 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
+  <conditionalFormatting sqref="C5:C34">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"매수"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"중립"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"매도"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="C5:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 값 확인" error="목록에서 선택: 매수 / 중립 / 매도" promptTitle="선택" prompt="매수 / 중립 / 매도 중 선택" type="list">
       <formula1>"매수,중립,매도"</formula1>
@@ -1465,6 +1594,22 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
+  <conditionalFormatting sqref="E5:E14">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"강세"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"중립"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"약세"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:G14">
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>AND($F5&lt;&gt;"",$G5&lt;&gt;"",$G5&lt;$F5)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="E5:E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 값 확인" error="목록에서 선택: 강세 / 중립 / 약세" promptTitle="선택" prompt="강세 / 중립 / 약세 중 선택" type="list">
       <formula1>"강세,중립,약세"</formula1>
